--- a/artfynd/A 7410-2024 artfynd.xlsx
+++ b/artfynd/A 7410-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7410-2024 artfynd.xlsx
+++ b/artfynd/A 7410-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87477516</v>
+        <v>98743379</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559958.1655503823</v>
+        <v>559981</v>
       </c>
       <c r="R2" t="n">
-        <v>6342572.257779126</v>
+        <v>6342574</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,22 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,63 +780,64 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98743375</v>
+        <v>98750536</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559966.3570088353</v>
+        <v>560101</v>
       </c>
       <c r="R3" t="n">
-        <v>6342568.586927193</v>
+        <v>6342560</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +867,9 @@
           <t>2022-02-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,54 +896,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98750570</v>
+        <v>87477734</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>Skog vid Tranhulta, Stenfloen, Berga, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560068.5524652915</v>
+        <v>559858</v>
       </c>
       <c r="R4" t="n">
-        <v>6342554.916667374</v>
+        <v>6342587</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,27 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera bestånd</t>
+          <t>2020-08-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,22 +998,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98743246</v>
+        <v>87477344</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,26 +1035,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>högsby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559959.6981297678</v>
+        <v>559944</v>
       </c>
       <c r="R5" t="n">
-        <v>6342578.777639465</v>
+        <v>6342610</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,22 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1152,10 +1104,1274 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87477421</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>560030</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6342582</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Jan Brenander</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87477469</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560037</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6342570</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87477493</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>559958</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6342593</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87477516</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>559958</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6342572</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>98743246</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>559959</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6342579</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>98743375</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>559966</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6342569</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>98743675</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>560030</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6342577</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>98743833</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>560010</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6342597</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>98750522</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>559961</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6342590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>98750526</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>560041</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6342576</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>99661330</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valåkra, Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>560211</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6342593</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-04-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-04-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>98750570</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>560069</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6342555</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flera bestånd</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7410-2024 artfynd.xlsx
+++ b/artfynd/A 7410-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98743379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98750536</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477469</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477493</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87477516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98743246</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98743375</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98743675</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98743833</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2060,6 +2125,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98750522</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98750526</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2265,6 +2340,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99661330</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,8 +2452,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98750570</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>